--- a/exclusion.xlsx
+++ b/exclusion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emery\Desktop\code\HtmlDocGenerator\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF12CB2-79ED-457D-AB05-692668C3F490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A240A599-D743-48EB-8C53-1C930B4DD494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="-15480" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hors analyse" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
   <si>
     <t>type</t>
   </si>
@@ -110,6 +110,48 @@
   </si>
   <si>
     <t>IAsyncTask</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Approval Submission</t>
+  </si>
+  <si>
+    <t>CalculationMatrix</t>
+  </si>
+  <si>
+    <t>CalculationMatrixActionLog</t>
+  </si>
+  <si>
+    <t>CalculationMatrixColumn</t>
+  </si>
+  <si>
+    <t>CalculationMatrixRow</t>
+  </si>
+  <si>
+    <t>CalculationMatrixVersion</t>
+  </si>
+  <si>
+    <t>CalculationProcedure</t>
+  </si>
+  <si>
+    <t>CalculationProcedureStep</t>
+  </si>
+  <si>
+    <t>CalculationProcedureVariable</t>
+  </si>
+  <si>
+    <t>CalculationProcedureVersion</t>
+  </si>
+  <si>
+    <t>DevopsActivityLog</t>
+  </si>
+  <si>
+    <t>DevopsEnvironment</t>
+  </si>
+  <si>
+    <t>DevopsRequestInfo</t>
   </si>
 </sst>
 </file>
@@ -450,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="48.90625" customWidth="1"/>
@@ -492,7 +534,7 @@
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -500,7 +542,7 @@
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
@@ -508,7 +550,7 @@
       <c r="A7" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -516,7 +558,7 @@
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -524,7 +566,7 @@
       <c r="A9" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -532,7 +574,7 @@
       <c r="A10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -540,7 +582,7 @@
       <c r="A11" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -548,7 +590,7 @@
       <c r="A12" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -556,7 +598,7 @@
       <c r="A13" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -564,7 +606,7 @@
       <c r="A14" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
@@ -572,7 +614,7 @@
       <c r="A15" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
@@ -580,7 +622,7 @@
       <c r="A16" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
@@ -588,7 +630,7 @@
       <c r="A17" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
@@ -596,7 +638,7 @@
       <c r="A18" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -604,7 +646,7 @@
       <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -612,7 +654,7 @@
       <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
@@ -620,7 +662,7 @@
       <c r="A21" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -628,7 +670,7 @@
       <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
@@ -636,7 +678,7 @@
       <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
@@ -644,7 +686,7 @@
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
@@ -652,7 +694,7 @@
       <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
@@ -660,7 +702,7 @@
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
@@ -668,7 +710,7 @@
       <c r="A27" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
@@ -676,8 +718,112 @@
       <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
